--- a/Assets/@Resources/Data/Excel/ComboData.xlsx
+++ b/Assets/@Resources/Data/Excel/ComboData.xlsx
@@ -598,7 +598,7 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>#8AFF6F</t>
+          <t>#00FF00</t>
         </is>
       </c>
     </row>
@@ -628,7 +628,7 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>#6FE3FF</t>
+          <t>#0067FF</t>
         </is>
       </c>
     </row>
@@ -658,7 +658,7 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>#8A6FFF</t>
+          <t>#9600FF</t>
         </is>
       </c>
     </row>
@@ -688,7 +688,7 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>#FF6FD8</t>
+          <t>#C58C00</t>
         </is>
       </c>
     </row>
@@ -718,7 +718,7 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>#FFC36F</t>
+          <t>#FFFF06</t>
         </is>
       </c>
     </row>
@@ -748,7 +748,7 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>#FF3E3E</t>
+          <t>#C00900</t>
         </is>
       </c>
     </row>
